--- a/site/exports/seu-cs.xlsx
+++ b/site/exports/seu-cs.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rebf391b0752148dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="R2d0297316b8e4c92"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="Rcb165914e9834efa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="Rbe9cc55573e24480"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R96f81a4c42ed4175"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R5c51a380c90e4088"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="Rfa220eb85b4e40d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="R2d119ef324e545bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R50e543e7a0e7480a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R67270ce7c72245d8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T38_0" displayName="T38_0" ref="A1:K2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T42_0" displayName="T42_0" ref="A1:K3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="校区"/>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T38_1" displayName="T38_1" ref="A1:S4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T42_1" displayName="T42_1" ref="A1:S8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="事件类型"/>
@@ -185,7 +185,27 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T38_3" displayName="T38_3" ref="A1:L2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T42_2" displayName="T42_2" ref="A1:L3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="12">
+    <x:tableColumn id="1" name="姓名"/>
+    <x:tableColumn id="2" name="导师姓名"/>
+    <x:tableColumn id="3" name="关系类型"/>
+    <x:tableColumn id="4" name="阶段"/>
+    <x:tableColumn id="5" name="简介"/>
+    <x:tableColumn id="6" name="在职状态"/>
+    <x:tableColumn id="7" name="状态说明"/>
+    <x:tableColumn id="8" name="已核在职主页"/>
+    <x:tableColumn id="9" name="关系来源"/>
+    <x:tableColumn id="10" name="任职来源"/>
+    <x:tableColumn id="11" name="所属学校ID"/>
+    <x:tableColumn id="12" name="所属学校"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T42_3" displayName="T42_3" ref="A1:L3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="标题"/>
@@ -204,8 +224,8 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T38_4" displayName="T38_4" ref="A1:G6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T42_4" displayName="T42_4" ref="A1:G13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="来源ID"/>
@@ -495,10 +515,43 @@
         <x:v>东南大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="3" ht="64" customHeight="1">
+      <x:c r="A3" s="6" t="str">
+        <x:v>白如帆</x:v>
+      </x:c>
+      <x:c r="B3" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C3" s="6" t="str">
+        <x:v>计算机科学与工程学院</x:v>
+      </x:c>
+      <x:c r="D3" s="6" t="str">
+        <x:v>https://cse.seu.edu.cn/2024/0117/c48203a479350/page.htm</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F3" s="6" t="str">
+        <x:v>无证字段不推断。；精选成果非全集。；本科未披露。</x:v>
+      </x:c>
+      <x:c r="G3" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H3" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I3" s="6" t="str"/>
+      <x:c r="J3" s="6" t="str">
+        <x:v>seu</x:v>
+      </x:c>
+      <x:c r="K3" s="6" t="str">
+        <x:v>东南大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f4e25df44064f52"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa33a2e5de534669"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -732,10 +785,190 @@
         <x:v>东南大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="5" ht="64" customHeight="1">
+      <x:c r="A5" s="6" t="str">
+        <x:v>白如帆</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C5" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D5" s="6" t="str">
+        <x:v>复旦大学</x:v>
+      </x:c>
+      <x:c r="E5" s="6" t="str"/>
+      <x:c r="F5" s="6" t="str">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="G5" s="6" t="str"/>
+      <x:c r="H5" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I5" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J5" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K5" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L5" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M5" s="7" t="str"/>
+      <x:c r="N5" s="6" t="str"/>
+      <x:c r="O5" s="6" t="str">
+        <x:v>本人明确取得硕士。</x:v>
+      </x:c>
+      <x:c r="P5" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q5" s="6" t="str">
+        <x:v>https://cse.seu.edu.cn/2024/0117/c48203a479350/page.htm</x:v>
+      </x:c>
+      <x:c r="R5" s="6" t="str">
+        <x:v>seu</x:v>
+      </x:c>
+      <x:c r="S5" s="6" t="str">
+        <x:v>东南大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="64" customHeight="1">
+      <x:c r="A6" s="6" t="str">
+        <x:v>白如帆</x:v>
+      </x:c>
+      <x:c r="B6" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C6" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="str">
+        <x:v>澳门大学</x:v>
+      </x:c>
+      <x:c r="E6" s="6" t="str"/>
+      <x:c r="F6" s="6" t="str">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="G6" s="6" t="str"/>
+      <x:c r="H6" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I6" s="6" t="str">
+        <x:v>中国澳门</x:v>
+      </x:c>
+      <x:c r="J6" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K6" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L6" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M6" s="7" t="str"/>
+      <x:c r="N6" s="6" t="str"/>
+      <x:c r="O6" s="6" t="str">
+        <x:v>本人明确取得博士；专业未由院系名推定。</x:v>
+      </x:c>
+      <x:c r="P6" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q6" s="6" t="str">
+        <x:v>https://cse.seu.edu.cn/2024/0117/c48203a479350/page.htm</x:v>
+      </x:c>
+      <x:c r="R6" s="6" t="str">
+        <x:v>seu</x:v>
+      </x:c>
+      <x:c r="S6" s="6" t="str">
+        <x:v>东南大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="64" customHeight="1">
+      <x:c r="A7" s="6" t="str">
+        <x:v>白如帆</x:v>
+      </x:c>
+      <x:c r="B7" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C7" s="6" t="str">
+        <x:v>讲师</x:v>
+      </x:c>
+      <x:c r="D7" s="6" t="str">
+        <x:v>东南大学计算机科学与工程学院</x:v>
+      </x:c>
+      <x:c r="E7" s="6" t="str">
+        <x:v>2023-09</x:v>
+      </x:c>
+      <x:c r="F7" s="6" t="str"/>
+      <x:c r="G7" s="6" t="str"/>
+      <x:c r="H7" s="6" t="str"/>
+      <x:c r="I7" s="6" t="str"/>
+      <x:c r="J7" s="6" t="str"/>
+      <x:c r="K7" s="6" t="str"/>
+      <x:c r="L7" s="6" t="str"/>
+      <x:c r="M7" s="7" t="str"/>
+      <x:c r="N7" s="6" t="str"/>
+      <x:c r="O7" s="6" t="str">
+        <x:v>本人明确2023.09加入；职称起始与入职合并仅按本人简介。</x:v>
+      </x:c>
+      <x:c r="P7" s="6" t="str"/>
+      <x:c r="Q7" s="6" t="str">
+        <x:v>https://cse.seu.edu.cn/2024/0117/c48203a479350/page.htm</x:v>
+      </x:c>
+      <x:c r="R7" s="6" t="str">
+        <x:v>seu</x:v>
+      </x:c>
+      <x:c r="S7" s="6" t="str">
+        <x:v>东南大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="64" customHeight="1">
+      <x:c r="A8" s="6" t="str">
+        <x:v>白如帆</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="str">
+        <x:v>强化学习见习研究员</x:v>
+      </x:c>
+      <x:c r="D8" s="6" t="str">
+        <x:v>上海人工智能实验室</x:v>
+      </x:c>
+      <x:c r="E8" s="6" t="str">
+        <x:v>2022-11</x:v>
+      </x:c>
+      <x:c r="F8" s="6" t="str">
+        <x:v>2023-05</x:v>
+      </x:c>
+      <x:c r="G8" s="6" t="str"/>
+      <x:c r="H8" s="6" t="str"/>
+      <x:c r="I8" s="6" t="str"/>
+      <x:c r="J8" s="6" t="str"/>
+      <x:c r="K8" s="6" t="str"/>
+      <x:c r="L8" s="6" t="str"/>
+      <x:c r="M8" s="7" t="str"/>
+      <x:c r="N8" s="6" t="str"/>
+      <x:c r="O8" s="6" t="str"/>
+      <x:c r="P8" s="6" t="str"/>
+      <x:c r="Q8" s="6" t="str">
+        <x:v>https://cs.seu.edu.cn/rfbai/main.htm</x:v>
+      </x:c>
+      <x:c r="R8" s="6" t="str">
+        <x:v>seu</x:v>
+      </x:c>
+      <x:c r="S8" s="6" t="str">
+        <x:v>东南大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcfb228bda78943db"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6283da9b2ae4470"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -796,8 +1029,83 @@
         <x:v>所属学校</x:v>
       </x:c>
     </x:row>
+    <x:row r="2" ht="64" customHeight="1">
+      <x:c r="A2" s="6" t="str">
+        <x:v>白如帆</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="str">
+        <x:v>贾维嘉</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="str">
+        <x:v>博士导师</x:v>
+      </x:c>
+      <x:c r="D2" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="E2" s="6" t="str">
+        <x:v>本人简介直接明确澳门大学博士阶段导师，教授；现职未知。</x:v>
+      </x:c>
+      <x:c r="F2" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G2" s="6" t="str">
+        <x:v>本人链出官方介绍读取超时，不能确认现职或可达导航。</x:v>
+      </x:c>
+      <x:c r="H2" s="6" t="str"/>
+      <x:c r="I2" s="6" t="str">
+        <x:v>https://cse.seu.edu.cn/2024/0117/c48203a479350/page.htm</x:v>
+      </x:c>
+      <x:c r="J2" s="6" t="str">
+        <x:v>https://www.bnuaifn.cn/ScientificResearchTeam/info_itemid_147_lcid_8.html</x:v>
+      </x:c>
+      <x:c r="K2" s="6" t="str">
+        <x:v>seu</x:v>
+      </x:c>
+      <x:c r="L2" s="6" t="str">
+        <x:v>东南大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="64" customHeight="1">
+      <x:c r="A3" s="6" t="str">
+        <x:v>白如帆</x:v>
+      </x:c>
+      <x:c r="B3" s="6" t="str">
+        <x:v>吴晓伟</x:v>
+      </x:c>
+      <x:c r="C3" s="6" t="str">
+        <x:v>博士导师</x:v>
+      </x:c>
+      <x:c r="D3" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="E3" s="6" t="str">
+        <x:v>本人简介明确澳门大学博士导师；其本人主页现自述澳门大学副教授。</x:v>
+      </x:c>
+      <x:c r="F3" s="6" t="str">
+        <x:v>self_reported_current_appointment</x:v>
+      </x:c>
+      <x:c r="G3" s="6" t="str">
+        <x:v>SEU本人链出该主页；澳门大学官方主页本次503，现职仅本人自述。</x:v>
+      </x:c>
+      <x:c r="H3" s="6" t="str"/>
+      <x:c r="I3" s="6" t="str">
+        <x:v>https://cse.seu.edu.cn/2024/0117/c48203a479350/page.htm</x:v>
+      </x:c>
+      <x:c r="J3" s="6" t="str">
+        <x:v>https://sites.google.com/site/wxw0711/</x:v>
+      </x:c>
+      <x:c r="K3" s="6" t="str">
+        <x:v>seu</x:v>
+      </x:c>
+      <x:c r="L3" s="6" t="str">
+        <x:v>东南大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61ca5faa612d459f"/>
+  </x:tableParts>
 </x:worksheet>
 </file>
 
@@ -891,10 +1199,46 @@
         <x:v>东南大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="3" ht="64" customHeight="1">
+      <x:c r="A3" s="6" t="str">
+        <x:v>白如帆</x:v>
+      </x:c>
+      <x:c r="B3" s="6" t="str">
+        <x:v>Multi-agent Online Scheduling: MMS Allocations for Indivisible Items</x:v>
+      </x:c>
+      <x:c r="C3" s="6" t="n">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="D3" s="6" t="str"/>
+      <x:c r="E3" s="6" t="str">
+        <x:v>https://proceedings.mlr.press/v202/zhou23a.html</x:v>
+      </x:c>
+      <x:c r="F3" s="6" t="str">
+        <x:v>会议论文；conference_paper</x:v>
+      </x:c>
+      <x:c r="G3" s="6" t="str">
+        <x:v>https://proceedings.mlr.press/v202/zhou23a.html</x:v>
+      </x:c>
+      <x:c r="H3" s="6" t="str">
+        <x:v>https://cs.seu.edu.cn/rfbai/main.htm</x:v>
+      </x:c>
+      <x:c r="I3" s="6" t="str">
+        <x:v>出版社文章元数据已核，不表示全文已读。；article_metadata_verified</x:v>
+      </x:c>
+      <x:c r="J3" s="6" t="str">
+        <x:v>本人官网列同题/同作者，PMLR直接核202:42506–42516；非全文。</x:v>
+      </x:c>
+      <x:c r="K3" s="6" t="str">
+        <x:v>seu</x:v>
+      </x:c>
+      <x:c r="L3" s="6" t="str">
+        <x:v>东南大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc114f0cadfc24d54"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19113c3db6e44728"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1050,10 +1394,171 @@
         <x:v>东南大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="7" ht="64" customHeight="1">
+      <x:c r="A7" s="6" t="str">
+        <x:v>白如帆</x:v>
+      </x:c>
+      <x:c r="B7" s="6" t="str">
+        <x:v>bairufan-source-1</x:v>
+      </x:c>
+      <x:c r="C7" s="6" t="str">
+        <x:v>https://cse.seu.edu.cn/szdw_48203/list.htm</x:v>
+      </x:c>
+      <x:c r="D7" s="6" t="str">
+        <x:v>官方名录内容已读，仅保存本批选中观察。；official_roster_read</x:v>
+      </x:c>
+      <x:c r="E7" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F7" s="6" t="str">
+        <x:v>seu</x:v>
+      </x:c>
+      <x:c r="G7" s="6" t="str">
+        <x:v>东南大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="64" customHeight="1">
+      <x:c r="A8" s="6" t="str">
+        <x:v>白如帆</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="str">
+        <x:v>bairufan-source-2</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="str">
+        <x:v>https://cse.seu.edu.cn/2024/0117/c48203a479350/page.htm</x:v>
+      </x:c>
+      <x:c r="D8" s="6" t="str">
+        <x:v>官方公开正文已读，仅覆盖已审字段。；official_public_body_read</x:v>
+      </x:c>
+      <x:c r="E8" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F8" s="6" t="str">
+        <x:v>seu</x:v>
+      </x:c>
+      <x:c r="G8" s="6" t="str">
+        <x:v>东南大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="64" customHeight="1">
+      <x:c r="A9" s="6" t="str">
+        <x:v>白如帆</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="str">
+        <x:v>bairufan-source-3</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="str">
+        <x:v>https://cs.seu.edu.cn/rfbai/main.htm</x:v>
+      </x:c>
+      <x:c r="D9" s="6" t="str">
+        <x:v>官方公开正文已读，仅覆盖已审字段。；official_public_body_read</x:v>
+      </x:c>
+      <x:c r="E9" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F9" s="6" t="str">
+        <x:v>seu</x:v>
+      </x:c>
+      <x:c r="G9" s="6" t="str">
+        <x:v>东南大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="64" customHeight="1">
+      <x:c r="A10" s="6" t="str">
+        <x:v>白如帆</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="str">
+        <x:v>bairufan-source-4</x:v>
+      </x:c>
+      <x:c r="C10" s="6" t="str">
+        <x:v>https://www.bnuaifn.cn/ScientificResearchTeam/info_itemid_147_lcid_8.html</x:v>
+      </x:c>
+      <x:c r="D10" s="6" t="str">
+        <x:v>目标读取超时，未取得该页正文。；timeout_not_read</x:v>
+      </x:c>
+      <x:c r="E10" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F10" s="6" t="str">
+        <x:v>seu</x:v>
+      </x:c>
+      <x:c r="G10" s="6" t="str">
+        <x:v>东南大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="64" customHeight="1">
+      <x:c r="A11" s="6" t="str">
+        <x:v>白如帆</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="str">
+        <x:v>bairufan-source-5</x:v>
+      </x:c>
+      <x:c r="C11" s="6" t="str">
+        <x:v>https://sites.google.com/site/wxw0711/</x:v>
+      </x:c>
+      <x:c r="D11" s="6" t="str">
+        <x:v>本人公开职业网站自述，非学校门户正文或人事核验。；self_authored_professional_profile_read</x:v>
+      </x:c>
+      <x:c r="E11" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F11" s="6" t="str">
+        <x:v>seu</x:v>
+      </x:c>
+      <x:c r="G11" s="6" t="str">
+        <x:v>东南大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="64" customHeight="1">
+      <x:c r="A12" s="6" t="str">
+        <x:v>白如帆</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="str">
+        <x:v>bairufan-source-6</x:v>
+      </x:c>
+      <x:c r="C12" s="6" t="str">
+        <x:v>https://proceedings.mlr.press/v202/zhou23a.html</x:v>
+      </x:c>
+      <x:c r="D12" s="6" t="str">
+        <x:v>出版社元数据已读，不表示全文已读。；publisher_metadata_read</x:v>
+      </x:c>
+      <x:c r="E12" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F12" s="6" t="str">
+        <x:v>seu</x:v>
+      </x:c>
+      <x:c r="G12" s="6" t="str">
+        <x:v>东南大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="64" customHeight="1">
+      <x:c r="A13" s="6" t="str">
+        <x:v>白如帆</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="str">
+        <x:v>institution-classification-6</x:v>
+      </x:c>
+      <x:c r="C13" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D13" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E13" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F13" s="6" t="str">
+        <x:v>seu</x:v>
+      </x:c>
+      <x:c r="G13" s="6" t="str">
+        <x:v>东南大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R83a4efa0c76c4160"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c674fbcb06d4910"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/exports/seu-cs.xlsx
+++ b/site/exports/seu-cs.xlsx
@@ -452,7 +452,7 @@
     <col width="65" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
-    <col width="18.2" customWidth="1" min="7" max="7"/>
+    <col width="37.8" customWidth="1" min="7" max="7"/>
     <col width="30.8" customWidth="1" min="8" max="8"/>
     <col width="65" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
@@ -482,7 +482,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>核对日期</t>
+          <t>已记录来源检索日期</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -545,7 +545,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -602,12 +602,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
